--- a/point_01/result/result.xlsx
+++ b/point_01/result/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bennkyou\Paper\atsukko-ego\atsukko-ego\point_01\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C5FB4D-1058-4C61-A7ED-1E41A02E834A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45632C4C-50A7-4A9B-B80B-C52600206476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -513,7 +513,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="C2" s="7">
         <v>48.28</v>

--- a/point_01/result/result.xlsx
+++ b/point_01/result/result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bennkyou\Paper\atsukko-ego\atsukko-ego\point_01\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45632C4C-50A7-4A9B-B80B-C52600206476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7585CCC7-18A3-478B-A7AD-D4D933D5052D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="1590" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>FRAME</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NPP(%,↑)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MPJPE(mm,↓)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -47,43 +43,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MPE(mm,↓)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>FS@0.1m(cm/s,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>↓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PA-MPJPE(mm↓)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Jitter(mm↓)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>36.80</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,15 +55,130 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.0320</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9280</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Inference(ms,↓)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93.00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRAME + GraphConv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36.41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRAME + TemperatureGraphConv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRAME + SpacialTemporalAttention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>91.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38.72</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47.78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>47.38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空间固定，时间可学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空间、时间可学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定邻接矩阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35.50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92.94</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnrealEgo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EgoPoseFormer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EgoWholeMocap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Egoglass</t>
+  </si>
+  <si>
+    <t>63.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EgoPW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRAME + LGC + JATS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FRAME + LGC </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRAME + JATS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.91</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,8 +210,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
+      <family val="1"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -166,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -174,9 +252,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -191,6 +266,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -471,42 +551,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
+    <col min="1" max="1" width="33.125" style="3" customWidth="1"/>
     <col min="2" max="11" width="17.5" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
-        <v>13</v>
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -515,60 +589,313 @@
       <c r="B2" s="4">
         <v>2.83</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>48.28</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8">
-        <v>3.2099999999999997E-2</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.91410000000000002</v>
-      </c>
-      <c r="H2" s="7">
-        <v>48.28</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>2.65</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>47.78</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>37.29</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>93.04</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0.91410000000000002</v>
-      </c>
-      <c r="H3" s="7">
-        <v>47.78</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0.9304</v>
-      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="10">
+        <v>36.85</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="10">
+        <v>52.34</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="10">
+        <v>3.02</v>
+      </c>
+      <c r="C8" s="10">
+        <v>48.81</v>
+      </c>
+      <c r="D8" s="10">
+        <v>36.01</v>
+      </c>
+      <c r="E8" s="10">
+        <v>92.81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="10">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="C9" s="10">
+        <v>48.34</v>
+      </c>
+      <c r="D9" s="10">
+        <v>35.78</v>
+      </c>
+      <c r="E9" s="10">
+        <v>92.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="10">
+        <v>3.44</v>
+      </c>
+      <c r="C10" s="10">
+        <v>49.75</v>
+      </c>
+      <c r="D10" s="10">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="E10" s="10">
+        <v>92.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="C12" s="6">
+        <v>48.28</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10">
+        <v>47.84</v>
+      </c>
+      <c r="D13" s="10">
+        <v>35.630000000000003</v>
+      </c>
+      <c r="E13" s="10">
+        <v>92.98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
+        <v>48.44</v>
+      </c>
+      <c r="D14" s="6">
+        <v>35.869999999999997</v>
+      </c>
+      <c r="E14" s="6">
+        <v>92.81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10">
+        <v>47.72</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="6">
+        <v>125.63</v>
+      </c>
+      <c r="D18" s="6">
+        <v>76.55</v>
+      </c>
+      <c r="E18" s="6">
+        <v>60.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="6">
+        <v>8.52</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>72.05</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="C20" s="4">
+        <v>112.46</v>
+      </c>
+      <c r="D20" s="4">
+        <v>69.87</v>
+      </c>
+      <c r="E20" s="4">
+        <v>59.31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="4">
+        <v>13.32</v>
+      </c>
+      <c r="C21" s="4">
+        <v>70.150000000000006</v>
+      </c>
+      <c r="D21" s="4">
+        <v>43.96</v>
+      </c>
+      <c r="E21" s="4">
+        <v>75.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="4">
+        <v>15.25</v>
+      </c>
+      <c r="C22" s="4">
+        <v>66.819999999999993</v>
+      </c>
+      <c r="D22" s="4">
+        <v>38.159999999999997</v>
+      </c>
+      <c r="E22" s="4">
+        <v>79.63</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
